--- a/uloha27/uloha27.xlsx
+++ b/uloha27/uloha27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF636A8-2AA6-4B93-ADBE-FA4760118641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B002A34-01E7-440F-B1A2-37EB8F4D39BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{635767DE-D7BD-46F5-96D6-3D4DDDEDB1B5}"/>
   </bookViews>
@@ -1059,7 +1059,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="cs-CZ"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3311,7 +3311,7 @@
         <v>1.5199999999999998</v>
       </c>
       <c r="D3">
-        <f>C3/1000/(A3*$E$1)*10^12</f>
+        <f t="shared" ref="D3:D13" si="0">C3/1000/(A3*$E$1)*10^12</f>
         <v>232.611070938567</v>
       </c>
       <c r="E3">
@@ -3327,7 +3327,7 @@
         <v>1.52</v>
       </c>
       <c r="H3">
-        <f>G3/B3*C3</f>
+        <f t="shared" ref="H3:H13" si="1">G3/B3*C3</f>
         <v>1.5199999999999998E-2</v>
       </c>
       <c r="I3">
@@ -3343,31 +3343,31 @@
         <v>164</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C13" si="0">B4/1000/100*1000</f>
+        <f t="shared" ref="C4:C13" si="2">B4/1000/100*1000</f>
         <v>1.64</v>
       </c>
       <c r="D4">
-        <f>C4/1000/(A4*$E$1)*10^12</f>
+        <f t="shared" si="0"/>
         <v>233.04830979371471</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E13" si="1">$D$14</f>
+        <f t="shared" ref="E4:E13" si="3">$D$14</f>
         <v>232.78485201295268</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F13" si="2">0.01*A4</f>
+        <f t="shared" ref="F4:F13" si="4">0.01*A4</f>
         <v>0.11199999999999999</v>
       </c>
       <c r="G4">
-        <f>0.01*B4</f>
+        <f t="shared" ref="G4:G13" si="5">0.01*B4</f>
         <v>1.6400000000000001</v>
       </c>
       <c r="H4">
-        <f>G4/B4*C4</f>
+        <f t="shared" si="1"/>
         <v>1.6399999999999998E-2</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I13" si="3">D4*SQRT(SUMSQ(H4/C4,F4/A4,$F$1/$E$1))</f>
+        <f t="shared" ref="I4:I13" si="6">D4*SQRT(SUMSQ(H4/C4,F4/A4,$F$1/$E$1))</f>
         <v>3.3040300322846874</v>
       </c>
     </row>
@@ -3379,31 +3379,31 @@
         <v>180</v>
       </c>
       <c r="C5">
+        <f t="shared" si="2"/>
+        <v>1.8</v>
+      </c>
+      <c r="D5">
         <f t="shared" si="0"/>
+        <v>234.81876876455863</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="3"/>
+        <v>232.78485201295268</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="4"/>
+        <v>0.122</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="5"/>
         <v>1.8</v>
       </c>
-      <c r="D5">
-        <f>C5/1000/(A5*$E$1)*10^12</f>
-        <v>234.81876876455863</v>
-      </c>
-      <c r="E5">
+      <c r="H5">
         <f t="shared" si="1"/>
-        <v>232.78485201295268</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="2"/>
-        <v>0.122</v>
-      </c>
-      <c r="G5">
-        <f>0.01*B5</f>
-        <v>1.8</v>
-      </c>
-      <c r="H5">
-        <f>G5/B5*C5</f>
         <v>1.8000000000000002E-2</v>
       </c>
       <c r="I5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.3291306202948472</v>
       </c>
     </row>
@@ -3415,31 +3415,31 @@
         <v>194</v>
       </c>
       <c r="C6">
+        <f t="shared" si="2"/>
+        <v>1.9400000000000002</v>
+      </c>
+      <c r="D6">
         <f t="shared" si="0"/>
-        <v>1.9400000000000002</v>
-      </c>
-      <c r="D6">
-        <f>C6/1000/(A6*$E$1)*10^12</f>
         <v>233.90953784173288</v>
       </c>
       <c r="E6">
+        <f t="shared" si="3"/>
+        <v>232.78485201295268</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="4"/>
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="5"/>
+        <v>1.94</v>
+      </c>
+      <c r="H6">
         <f t="shared" si="1"/>
-        <v>232.78485201295268</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="2"/>
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="G6">
-        <f>0.01*B6</f>
-        <v>1.94</v>
-      </c>
-      <c r="H6">
-        <f>G6/B6*C6</f>
         <v>1.9400000000000001E-2</v>
       </c>
       <c r="I6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.3162400471859614</v>
       </c>
     </row>
@@ -3451,31 +3451,31 @@
         <v>208</v>
       </c>
       <c r="C7">
+        <f t="shared" si="2"/>
+        <v>2.0799999999999996</v>
+      </c>
+      <c r="D7">
         <f t="shared" si="0"/>
-        <v>2.0799999999999996</v>
-      </c>
-      <c r="D7">
-        <f>C7/1000/(A7*$E$1)*10^12</f>
         <v>233.12836761226285</v>
       </c>
       <c r="E7">
+        <f t="shared" si="3"/>
+        <v>232.78485201295268</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="4"/>
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="5"/>
+        <v>2.08</v>
+      </c>
+      <c r="H7">
         <f t="shared" si="1"/>
-        <v>232.78485201295268</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="2"/>
-        <v>0.14199999999999999</v>
-      </c>
-      <c r="G7">
-        <f>0.01*B7</f>
-        <v>2.08</v>
-      </c>
-      <c r="H7">
-        <f>G7/B7*C7</f>
         <v>2.0799999999999996E-2</v>
       </c>
       <c r="I7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.3051650477543828</v>
       </c>
     </row>
@@ -3487,31 +3487,31 @@
         <v>224</v>
       </c>
       <c r="C8">
+        <f t="shared" si="2"/>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="D8">
         <f t="shared" si="0"/>
+        <v>234.54412692974626</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="3"/>
+        <v>232.78485201295268</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="4"/>
+        <v>0.152</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="5"/>
         <v>2.2400000000000002</v>
       </c>
-      <c r="D8">
-        <f>C8/1000/(A8*$E$1)*10^12</f>
-        <v>234.54412692974626</v>
-      </c>
-      <c r="E8">
+      <c r="H8">
         <f t="shared" si="1"/>
-        <v>232.78485201295268</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="2"/>
-        <v>0.152</v>
-      </c>
-      <c r="G8">
-        <f>0.01*B8</f>
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="H8">
-        <f>G8/B8*C8</f>
         <v>2.2400000000000003E-2</v>
       </c>
       <c r="I8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.32523690027111</v>
       </c>
     </row>
@@ -3523,31 +3523,31 @@
         <v>238</v>
       </c>
       <c r="C9">
+        <f t="shared" si="2"/>
+        <v>2.38</v>
+      </c>
+      <c r="D9">
         <f t="shared" si="0"/>
+        <v>233.82022530341982</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="3"/>
+        <v>232.78485201295268</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="4"/>
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="5"/>
         <v>2.38</v>
       </c>
-      <c r="D9">
-        <f>C9/1000/(A9*$E$1)*10^12</f>
-        <v>233.82022530341982</v>
-      </c>
-      <c r="E9">
+      <c r="H9">
         <f t="shared" si="1"/>
-        <v>232.78485201295268</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="2"/>
-        <v>0.16200000000000001</v>
-      </c>
-      <c r="G9">
-        <f>0.01*B9</f>
-        <v>2.38</v>
-      </c>
-      <c r="H9">
-        <f>G9/B9*C9</f>
         <v>2.3799999999999998E-2</v>
       </c>
       <c r="I9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.3149738234184207</v>
       </c>
     </row>
@@ -3559,31 +3559,31 @@
         <v>254</v>
       </c>
       <c r="C10">
+        <f t="shared" si="2"/>
+        <v>2.54</v>
+      </c>
+      <c r="D10">
         <f t="shared" si="0"/>
+        <v>232.329629836403</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="3"/>
+        <v>232.78485201295268</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="4"/>
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="5"/>
         <v>2.54</v>
       </c>
-      <c r="D10">
-        <f>C10/1000/(A10*$E$1)*10^12</f>
-        <v>232.329629836403</v>
-      </c>
-      <c r="E10">
+      <c r="H10">
         <f t="shared" si="1"/>
-        <v>232.78485201295268</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="2"/>
-        <v>0.17399999999999999</v>
-      </c>
-      <c r="G10">
-        <f>0.01*B10</f>
-        <v>2.54</v>
-      </c>
-      <c r="H10">
-        <f>G10/B10*C10</f>
         <v>2.5400000000000002E-2</v>
       </c>
       <c r="I10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.2938409853670727</v>
       </c>
     </row>
@@ -3595,31 +3595,31 @@
         <v>268</v>
       </c>
       <c r="C11">
+        <f t="shared" si="2"/>
+        <v>2.68</v>
+      </c>
+      <c r="D11">
         <f t="shared" si="0"/>
+        <v>229.3200257922941</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="3"/>
+        <v>232.78485201295268</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="4"/>
+        <v>0.18600000000000003</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="5"/>
         <v>2.68</v>
       </c>
-      <c r="D11">
-        <f>C11/1000/(A11*$E$1)*10^12</f>
-        <v>229.3200257922941</v>
-      </c>
-      <c r="E11">
+      <c r="H11">
         <f t="shared" si="1"/>
-        <v>232.78485201295268</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="2"/>
-        <v>0.18600000000000003</v>
-      </c>
-      <c r="G11">
-        <f>0.01*B11</f>
-        <v>2.68</v>
-      </c>
-      <c r="H11">
-        <f>G11/B11*C11</f>
         <v>2.6800000000000001E-2</v>
       </c>
       <c r="I11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.251172483905624</v>
       </c>
     </row>
@@ -3631,31 +3631,31 @@
         <v>284</v>
       </c>
       <c r="C12">
+        <f t="shared" si="2"/>
+        <v>2.84</v>
+      </c>
+      <c r="D12">
         <f t="shared" si="0"/>
+        <v>230.61226474360615</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="3"/>
+        <v>232.78485201295268</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="4"/>
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="5"/>
         <v>2.84</v>
       </c>
-      <c r="D12">
-        <f>C12/1000/(A12*$E$1)*10^12</f>
-        <v>230.61226474360615</v>
-      </c>
-      <c r="E12">
+      <c r="H12">
         <f t="shared" si="1"/>
-        <v>232.78485201295268</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="2"/>
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="G12">
-        <f>0.01*B12</f>
-        <v>2.84</v>
-      </c>
-      <c r="H12">
-        <f>G12/B12*C12</f>
         <v>2.8399999999999998E-2</v>
       </c>
       <c r="I12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.2694931329925123</v>
       </c>
     </row>
@@ -3667,31 +3667,31 @@
         <v>298</v>
       </c>
       <c r="C13">
+        <f t="shared" si="2"/>
+        <v>2.98</v>
+      </c>
+      <c r="D13">
         <f t="shared" si="0"/>
+        <v>232.49104458617356</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>232.78485201295268</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="4"/>
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="5"/>
         <v>2.98</v>
       </c>
-      <c r="D13">
-        <f>C13/1000/(A13*$E$1)*10^12</f>
-        <v>232.49104458617356</v>
-      </c>
-      <c r="E13">
+      <c r="H13">
         <f t="shared" si="1"/>
-        <v>232.78485201295268</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="2"/>
-        <v>0.20399999999999999</v>
-      </c>
-      <c r="G13">
-        <f>0.01*B13</f>
-        <v>2.98</v>
-      </c>
-      <c r="H13">
-        <f>G13/B13*C13</f>
         <v>2.98E-2</v>
       </c>
       <c r="I13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.2961294344073928</v>
       </c>
     </row>
@@ -3781,18 +3781,18 @@
         <v>1.1038961038961039</v>
       </c>
       <c r="B23">
-        <f>B22+$C$20</f>
+        <f t="shared" ref="B23:B30" si="7">B22+$C$20</f>
         <v>0.90588235294117647</v>
       </c>
       <c r="C23">
         <v>442.4</v>
       </c>
       <c r="D23">
-        <f t="shared" ref="D23:D35" si="4">0.1/A23^2</f>
+        <f t="shared" ref="D23:D35" si="8">0.1/A23^2</f>
         <v>8.2062283737024219E-2</v>
       </c>
       <c r="E23">
-        <f t="shared" ref="E23:E36" si="5">0.005*C23</f>
+        <f t="shared" ref="E23:E36" si="9">0.005*C23</f>
         <v>2.2119999999999997</v>
       </c>
       <c r="G23">
@@ -3809,22 +3809,22 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
-        <f t="shared" ref="A24:A30" si="6">1/B24</f>
+        <f t="shared" ref="A24:A30" si="10">1/B24</f>
         <v>1.2318840579710144</v>
       </c>
       <c r="B24">
-        <f>B23+$C$20</f>
+        <f t="shared" si="7"/>
         <v>0.81176470588235294</v>
       </c>
       <c r="C24">
         <v>382.6</v>
       </c>
       <c r="D24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>6.589619377162631E-2</v>
       </c>
       <c r="E24">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.9130000000000003</v>
       </c>
       <c r="G24" s="1">
@@ -3841,22 +3841,22 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.3934426229508197</v>
       </c>
       <c r="B25">
-        <f>B24+$C$20</f>
+        <f t="shared" si="7"/>
         <v>0.71764705882352942</v>
       </c>
       <c r="C25">
         <v>353.2</v>
       </c>
       <c r="D25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>5.150173010380623E-2</v>
       </c>
       <c r="E25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.766</v>
       </c>
       <c r="G25">
@@ -3869,106 +3869,106 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.6037735849056605</v>
       </c>
       <c r="B26">
-        <f>B25+$C$20</f>
+        <f t="shared" si="7"/>
         <v>0.62352941176470589</v>
       </c>
       <c r="C26">
         <v>313</v>
       </c>
       <c r="D26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3.8878892733564013E-2</v>
       </c>
       <c r="E26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.5649999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.8888888888888888</v>
       </c>
       <c r="B27">
-        <f>B26+$C$20</f>
+        <f t="shared" si="7"/>
         <v>0.52941176470588236</v>
       </c>
       <c r="C27">
         <v>260.7</v>
       </c>
       <c r="D27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.8027681660899657E-2</v>
       </c>
       <c r="E27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.3034999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.2972972972972974</v>
       </c>
       <c r="B28">
-        <f>B27+$C$20</f>
+        <f t="shared" si="7"/>
         <v>0.43529411764705883</v>
       </c>
       <c r="C28">
         <v>215.2</v>
       </c>
       <c r="D28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.894809688581315E-2</v>
       </c>
       <c r="E28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.0760000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.9310344827586206</v>
       </c>
       <c r="B29">
-        <f>B28+$C$20</f>
+        <f t="shared" si="7"/>
         <v>0.3411764705882353</v>
       </c>
       <c r="C29">
         <v>166.4</v>
       </c>
       <c r="D29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.1640138408304501E-2</v>
       </c>
       <c r="E29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.83200000000000007</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4.0476190476190474</v>
       </c>
       <c r="B30">
-        <f>B29+$C$20</f>
+        <f t="shared" si="7"/>
         <v>0.24705882352941178</v>
       </c>
       <c r="C30">
         <v>121</v>
       </c>
       <c r="D30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>6.1038062283737034E-3</v>
       </c>
       <c r="E30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.60499999999999998</v>
       </c>
     </row>
@@ -3977,18 +3977,18 @@
         <v>6</v>
       </c>
       <c r="B31">
-        <f>1/A31</f>
+        <f t="shared" ref="B31:B36" si="11">1/A31</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="C31">
         <v>93.2</v>
       </c>
       <c r="D31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.7777777777777779E-3</v>
       </c>
       <c r="E31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.46600000000000003</v>
       </c>
     </row>
@@ -3997,18 +3997,18 @@
         <v>7</v>
       </c>
       <c r="B32">
-        <f>1/A32</f>
+        <f t="shared" si="11"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="C32">
         <v>81.8</v>
       </c>
       <c r="D32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.0408163265306124E-3</v>
       </c>
       <c r="E32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.40899999999999997</v>
       </c>
     </row>
@@ -4017,18 +4017,18 @@
         <v>10</v>
       </c>
       <c r="B33">
-        <f>1/A33</f>
+        <f t="shared" si="11"/>
         <v>0.1</v>
       </c>
       <c r="C33">
         <v>61.4</v>
       </c>
       <c r="D33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1E-3</v>
       </c>
       <c r="E33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.307</v>
       </c>
     </row>
@@ -4037,18 +4037,18 @@
         <v>17</v>
       </c>
       <c r="B34">
-        <f>1/A34</f>
+        <f t="shared" si="11"/>
         <v>5.8823529411764705E-2</v>
       </c>
       <c r="C34">
         <v>41.4</v>
       </c>
       <c r="D34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3.4602076124567478E-4</v>
       </c>
       <c r="E34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -4057,18 +4057,18 @@
         <v>25</v>
       </c>
       <c r="B35">
-        <f>1/A35</f>
+        <f t="shared" si="11"/>
         <v>0.04</v>
       </c>
       <c r="C35">
         <v>32</v>
       </c>
       <c r="D35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.6000000000000001E-4</v>
       </c>
       <c r="E35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.16</v>
       </c>
     </row>
@@ -4077,7 +4077,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <f>1/A36</f>
+        <f t="shared" si="11"/>
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="C36">
@@ -4088,7 +4088,7 @@
         <v>8.163265306122449E-5</v>
       </c>
       <c r="E36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.13100000000000001</v>
       </c>
     </row>
@@ -4165,22 +4165,22 @@
         <v>126.1</v>
       </c>
       <c r="E42">
-        <f t="shared" ref="E42:E45" si="7">C42/D42</f>
+        <f t="shared" ref="E42:E45" si="12">C42/D42</f>
         <v>2.8342585249801746</v>
       </c>
       <c r="F42">
         <v>0.1</v>
       </c>
       <c r="G42">
-        <f t="shared" ref="G42:G45" si="8">0.005*C42</f>
+        <f t="shared" ref="G42:G45" si="13">0.005*C42</f>
         <v>1.7869999999999999</v>
       </c>
       <c r="H42">
-        <f t="shared" ref="H42:H45" si="9">0.005*D42</f>
+        <f t="shared" ref="H42:H45" si="14">0.005*D42</f>
         <v>0.63049999999999995</v>
       </c>
       <c r="I42">
-        <f t="shared" ref="I42:I45" si="10">E42*SQRT(SUMSQ(G42/C42,H42/D42))</f>
+        <f t="shared" ref="I42:I45" si="15">E42*SQRT(SUMSQ(G42/C42,H42/D42))</f>
         <v>2.0041234226492632E-2</v>
       </c>
     </row>
@@ -4198,22 +4198,22 @@
         <v>77.5</v>
       </c>
       <c r="E43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.1251612903225805</v>
       </c>
       <c r="F43">
         <v>0.1</v>
       </c>
       <c r="G43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>0.82350000000000001</v>
       </c>
       <c r="H43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>0.38750000000000001</v>
       </c>
       <c r="I43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>1.50271595950225E-2</v>
       </c>
     </row>
@@ -4231,22 +4231,22 @@
         <v>74.2</v>
       </c>
       <c r="E44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.0498652291105119</v>
       </c>
       <c r="F44">
         <v>0.1</v>
       </c>
       <c r="G44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>0.76049999999999995</v>
       </c>
       <c r="H44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>0.371</v>
       </c>
       <c r="I44">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>1.449473604022559E-2</v>
       </c>
     </row>
@@ -4264,22 +4264,22 @@
         <v>74.7</v>
       </c>
       <c r="E45">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.0803212851405624</v>
       </c>
       <c r="F45">
         <v>0.1</v>
       </c>
       <c r="G45">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>0.77700000000000002</v>
       </c>
       <c r="H45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>0.3735</v>
       </c>
       <c r="I45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>1.4710092877696051E-2</v>
       </c>
     </row>

--- a/uloha27/uloha27.xlsx
+++ b/uloha27/uloha27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B002A34-01E7-440F-B1A2-37EB8F4D39BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A7D65D-3410-4DFD-9FDD-091DBC3825E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{635767DE-D7BD-46F5-96D6-3D4DDDEDB1B5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>U0 (V)</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>teor. eps0</t>
+  </si>
+  <si>
+    <t>materiál</t>
   </si>
 </sst>
 </file>
@@ -4093,6 +4096,9 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>31</v>
+      </c>
       <c r="B40" t="s">
         <v>3</v>
       </c>
